--- a/knowledge_base/source/08_recommendations.xlsx
+++ b/knowledge_base/source/08_recommendations.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_recommendations" sheetId="1" r:id="Rc31a5a3f1a384b23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_recommendations" sheetId="1" r:id="R5b4fd58a38c74ed0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1138,7 +1138,7 @@
         <x:v>Complete the Assessment Data</x:v>
       </x:c>
       <x:c r="D27" s="32" t="str">
-        <x:v>Provide readable assessment methods or activities needed for the requested comparison.</x:v>
+        <x:v>Provide readable assessment methods or activities required for the mandatory analysis.</x:v>
       </x:c>
       <x:c r="E27" s="32" t="str">
         <x:v>Partially Satisfied or Not Satisfied</x:v>
@@ -1150,7 +1150,7 @@
         <x:v>Input Correction</x:v>
       </x:c>
       <x:c r="H27" s="38" t="str">
-        <x:v>Not applicable when assessment comparison is not requested.</x:v>
+        <x:v>Assessment comparison is part of the mandatory full analysis.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="42" customHeight="1">
@@ -1384,13 +1384,13 @@
         <x:v>Input Request</x:v>
       </x:c>
       <x:c r="H36" s="41" t="str">
-        <x:v>Used only for requested assessment comparison.</x:v>
+        <x:v>Used when the required TP-153 assessment evidence is missing, incomplete, or unreadable.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d292570d39d49da"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf98c18215374fe2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/knowledge_base/source/08_recommendations.xlsx
+++ b/knowledge_base/source/08_recommendations.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_recommendations" sheetId="1" r:id="R5b4fd58a38c74ed0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_recommendations" sheetId="1" r:id="Ra1aa2ad4697442a2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -166,7 +166,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="42">
+  <x:cellXfs count="43">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -269,6 +269,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -771,10 +772,10 @@
         <x:v>RULE012</x:v>
       </x:c>
       <x:c r="C13" s="32" t="str">
-        <x:v>Remove Material Ambiguity</x:v>
+        <x:v>Clarify Ambiguous Wording</x:v>
       </x:c>
       <x:c r="D13" s="32" t="str">
-        <x:v>Clarify terminology conditions references and expected answer scope.</x:v>
+        <x:v>Clarify ambiguous terminology, contradictory wording, or response scope that permits materially different interpretations.</x:v>
       </x:c>
       <x:c r="E13" s="32" t="str">
         <x:v>Partially Satisfied or Not Satisfied</x:v>
@@ -786,7 +787,7 @@
         <x:v>Corrective</x:v>
       </x:c>
       <x:c r="H13" s="38" t="str">
-        <x:v>Focus only on ambiguity affecting answerability.</x:v>
+        <x:v>Do not use this recommendation solely because a clearly referenced supporting item is unavailable.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
@@ -800,7 +801,7 @@
         <x:v>Complete the Question Information</x:v>
       </x:c>
       <x:c r="D14" s="32" t="str">
-        <x:v>Add the missing data conditions assumptions or context necessary for answering.</x:v>
+        <x:v>Add the missing question-specific data, conditions, assumptions, or referenced context needed to answer the question.</x:v>
       </x:c>
       <x:c r="E14" s="32" t="str">
         <x:v>Partially Satisfied or Not Satisfied</x:v>
@@ -812,7 +813,7 @@
         <x:v>Corrective</x:v>
       </x:c>
       <x:c r="H14" s="38" t="str">
-        <x:v>Do not rely on unstated information.</x:v>
+        <x:v>Use confirmed question-specific context, including associated supporting material.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="42" customHeight="1">
@@ -1005,10 +1006,10 @@
         <x:v>RULE021</x:v>
       </x:c>
       <x:c r="C22" s="32" t="str">
-        <x:v>Complete the Instructions</x:v>
+        <x:v>Complete the General Exam Instructions</x:v>
       </x:c>
       <x:c r="D22" s="32" t="str">
-        <x:v>Add necessary instructions about answers resources tools or constraints.</x:v>
+        <x:v>Add necessary exam-level instructions about answer requirements, resources or tools, general constraints, or submission and formatting directions.</x:v>
       </x:c>
       <x:c r="E22" s="32" t="str">
         <x:v>Partially Satisfied or Not Satisfied</x:v>
@@ -1020,7 +1021,7 @@
         <x:v>Corrective</x:v>
       </x:c>
       <x:c r="H22" s="38" t="str">
-        <x:v>Do not add irrelevant instructions.</x:v>
+        <x:v>Do not use this recommendation for an incomplete individual question or unavailable supporting material.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="42" customHeight="1">
@@ -1343,10 +1344,10 @@
         <x:v>RULE021</x:v>
       </x:c>
       <x:c r="C35" s="32" t="str">
-        <x:v>Request Readable Instructions</x:v>
+        <x:v>Request Readable General Exam Instructions</x:v>
       </x:c>
       <x:c r="D35" s="32" t="str">
-        <x:v>Ask the user to provide a clearer exam copy when instruction text is unreadable.</x:v>
+        <x:v>Ask the user to provide a clearer exam copy when exam-level general instruction text is unreadable.</x:v>
       </x:c>
       <x:c r="E35" s="32" t="str">
         <x:v>Not Verified</x:v>
@@ -1358,7 +1359,7 @@
         <x:v>Input Request</x:v>
       </x:c>
       <x:c r="H35" s="38" t="str">
-        <x:v>Affected checks remain Not Verified.</x:v>
+        <x:v>Question-specific information remains outside RULE021.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="42" customHeight="1">
@@ -1390,7 +1391,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf98c18215374fe2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56414ac04d8d4770"/>
   </x:tableParts>
 </x:worksheet>
 </file>